--- a/Result/profitability/4426.xlsx
+++ b/Result/profitability/4426.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.51125</v>
+        <v>-0.49625</v>
       </c>
       <c r="N2" t="n">
-        <v>-7.6525</v>
+        <v>-7.55875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4087499999999999</v>
+        <v>-0.41875</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.84375</v>
+        <v>-2.037500000000001</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.31</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3174999999999999</v>
+        <v>-0.3375</v>
       </c>
       <c r="N4" t="n">
-        <v>3.47875</v>
+        <v>3.4475</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.52</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.21</v>
+        <v>-0.07749999999999997</v>
       </c>
       <c r="N5" t="n">
-        <v>9.5725</v>
+        <v>10.965</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02250000000000003</v>
+        <v>0.01250000000000002</v>
       </c>
       <c r="N6" t="n">
-        <v>16.75125</v>
+        <v>18.03875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07875000000000003</v>
+        <v>0.09250000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>23.95</v>
+        <v>25.7875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.21125</v>
+        <v>0.18375</v>
       </c>
       <c r="N8" t="n">
-        <v>32.39875</v>
+        <v>31.42125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.35375</v>
       </c>
       <c r="N10" t="n">
-        <v>39.16625000000001</v>
+        <v>39.16625</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>220</v>
+      </c>
+      <c r="D75" t="n">
+        <v>241</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-67</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-30.28%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-79</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-86</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.59375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-13.04875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7857142857142856</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>4.296703296703297</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6794871794871795</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.5360923965351299</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
